--- a/excel_sheeets/Avtar_Singh_mk.xlsx
+++ b/excel_sheeets/Avtar_Singh_mk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Author Details" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="145">
   <si>
     <t>Full Author Name</t>
   </si>
@@ -163,6 +163,318 @@
   </si>
   <si>
     <t>Mechanics</t>
+  </si>
+  <si>
+    <t>Journal of the Nepal Medical Association</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>Indian Farming</t>
+  </si>
+  <si>
+    <t>NISCAIR-CSIR, India</t>
+  </si>
+  <si>
+    <t>Proceedings of the Annual International Conference of the IEEE Engineering in Medicine and Biology Society Volume 13: 1991</t>
+  </si>
+  <si>
+    <t>Computer Science Review</t>
+  </si>
+  <si>
+    <t>Elsevier</t>
+  </si>
+  <si>
+    <t>Emergency Medicine Journal</t>
+  </si>
+  <si>
+    <t>British Association for Accident and Emergency Medicine</t>
+  </si>
+  <si>
+    <t>Springer US</t>
+  </si>
+  <si>
+    <t>Indian Journal of Soil Conservation</t>
+  </si>
+  <si>
+    <t>Indian Associations of Soil &amp; Water Conservationists</t>
+  </si>
+  <si>
+    <t>Journal of AgriSearch</t>
+  </si>
+  <si>
+    <t>Russian Journal of Plant Physiology</t>
+  </si>
+  <si>
+    <t>Pleiades Publishing</t>
+  </si>
+  <si>
+    <t>Indian Horticulture (India)</t>
+  </si>
+  <si>
+    <t>Journal of Computer and Communications</t>
+  </si>
+  <si>
+    <t>Scientific Research Publishing</t>
+  </si>
+  <si>
+    <t>Materials science and technology</t>
+  </si>
+  <si>
+    <t>SAGE Publications</t>
+  </si>
+  <si>
+    <t>International Journal of Cloud Applications and Computing (IJCAC)</t>
+  </si>
+  <si>
+    <t>IGI Global</t>
+  </si>
+  <si>
+    <t>Journal of communication studies</t>
+  </si>
+  <si>
+    <t>Metron</t>
+  </si>
+  <si>
+    <t>2018 First International Conference on Secure Cyber Computing and Communication (ICSCCC)</t>
+  </si>
+  <si>
+    <t>Internal Journal of Research in Commerce Management</t>
+  </si>
+  <si>
+    <t>Asian Journal of Management Research</t>
+  </si>
+  <si>
+    <t>Digital Business: Business Algorithms, Cloud Computing and Data Engineering</t>
+  </si>
+  <si>
+    <t>Springer International Publishing</t>
+  </si>
+  <si>
+    <t>Twelfth International Waste Management and Landfi ll Symposium, CISA, Environmental Santiary Engineering Centre, Italy Cagliari, Sardinia, Italy</t>
+  </si>
+  <si>
+    <t>Journal of the Indian Medical Association</t>
+  </si>
+  <si>
+    <t>Asian J of Pharmaceutical Technology &amp; Innovation</t>
+  </si>
+  <si>
+    <t>International Journal of Business Quantitative Economic and Applied Management Research</t>
+  </si>
+  <si>
+    <t>Int. J. Sci. Eng. Res</t>
+  </si>
+  <si>
+    <t>IEIE Transactions on Smart Processing and Computing</t>
+  </si>
+  <si>
+    <t>The Institute of Electronics and Information Engineers</t>
+  </si>
+  <si>
+    <t>Bentham Science Publishers</t>
+  </si>
+  <si>
+    <t>International Journal of Current Microbiology and Applied Sciences</t>
+  </si>
+  <si>
+    <t>Recent trends in biotechnology and microbiology. New York: Nova Science Publisher</t>
+  </si>
+  <si>
+    <t>International journal of chemical and analytical science</t>
+  </si>
+  <si>
+    <t>Plantation Crops-opportunities and constraints</t>
+  </si>
+  <si>
+    <t>Oxford and IBHP Pub. Co., New Delhi, India</t>
+  </si>
+  <si>
+    <t>Saraswati: The River par Excellence. The Asiatic Society, Kolkata</t>
+  </si>
+  <si>
+    <t>Metals Materials and Processes</t>
+  </si>
+  <si>
+    <t>Indian J Med Sci</t>
+  </si>
+  <si>
+    <t>DOI: https://doi. org/10.3390/ph15091071</t>
+  </si>
+  <si>
+    <t>Computational Intelligence and Healthcare Informatics</t>
+  </si>
+  <si>
+    <t>John Wiley &amp; Sons, Inc.</t>
+  </si>
+  <si>
+    <t>Indian Journal of Physics</t>
+  </si>
+  <si>
+    <t>Springer-Verlag</t>
+  </si>
+  <si>
+    <t>International Journal of Quantum Chemistry</t>
+  </si>
+  <si>
+    <t>Wiley Subscription Services, Inc., A Wiley Company</t>
+  </si>
+  <si>
+    <t>Journal de Physique-Colloques</t>
+  </si>
+  <si>
+    <t>Les Ulis: EDP Sciences, 1998-2006.</t>
+  </si>
+  <si>
+    <t>Proc. Indian Natl. Sci. Acad</t>
+  </si>
+  <si>
+    <t>J Health Sci</t>
+  </si>
+  <si>
+    <t>International Journal of Clinical Virology</t>
+  </si>
+  <si>
+    <t>Soft Computing: Theories and Applications: Proceedings of SoCTA 2018</t>
+  </si>
+  <si>
+    <t>Springer Singapore</t>
+  </si>
+  <si>
+    <t>International Journal of Computer Application</t>
+  </si>
+  <si>
+    <t>rspublication</t>
+  </si>
+  <si>
+    <t>Energy Sources, Part A: Recovery, Utilization, and Environmental Effects</t>
+  </si>
+  <si>
+    <t>Taylor &amp; Francis Group</t>
+  </si>
+  <si>
+    <t>S. Chand Publishing</t>
+  </si>
+  <si>
+    <t>Images of the Twenty-First Century. Proceedings of the Annual International Engineering in Medicine and Biology Society,</t>
+  </si>
+  <si>
+    <t>Proceedings of the International Conference on Paradigms of Computing, Communication and Data Sciences: PCCDS 2020</t>
+  </si>
+  <si>
+    <t>Springer Nature Singapore</t>
+  </si>
+  <si>
+    <t>International Conference on Advanced Communication and Computational Technology</t>
+  </si>
+  <si>
+    <t>Environment and Ecology</t>
+  </si>
+  <si>
+    <t>National Conference on Emerging Trends in Renewable Energy Technology-2012, Bhilwara, India</t>
+  </si>
+  <si>
+    <t>2011 IEEE International Instrumentation and Measurement Technology Conference</t>
+  </si>
+  <si>
+    <t>Biotechnol Genom Appl</t>
+  </si>
+  <si>
+    <t>Exploration and Research for Atomic Minerals</t>
+  </si>
+  <si>
+    <t>Deep Electromagnetic Exploration</t>
+  </si>
+  <si>
+    <t>Springer Berlin Heidelberg</t>
+  </si>
+  <si>
+    <t>Technometrics</t>
+  </si>
+  <si>
+    <t>International Journal of Ecology and Environmental Sciences</t>
+  </si>
+  <si>
+    <t>International Journal of Plant &amp; Soil Science</t>
+  </si>
+  <si>
+    <t>Optimization Methods for Engineering Problems</t>
+  </si>
+  <si>
+    <t>Apple Academic Press</t>
+  </si>
+  <si>
+    <t>2022 Algorithms, Computing and Mathematics Conference (ACM)</t>
+  </si>
+  <si>
+    <t>Plant Growth Regulators in Tropical and Sub-tropical Fruit Crops</t>
+  </si>
+  <si>
+    <t>CRC press</t>
+  </si>
+  <si>
+    <t>s Note: MDPI stays neutral with regard to jurisdictional claims in published maps and institutional affil-iations.</t>
+  </si>
+  <si>
+    <t>Soft Computing: Theories and Applications: Proceedings of SoCTA 2020, Volume 1</t>
+  </si>
+  <si>
+    <t>International Journal of Advanced Remote Sensing and GIS</t>
+  </si>
+  <si>
+    <t>Journal of Pharmacognosy and Phytochemistry</t>
+  </si>
+  <si>
+    <t>AkiNik Publications</t>
+  </si>
+  <si>
+    <t>International Journal of Business Quantitative Economics and Applied Management Research</t>
+  </si>
+  <si>
+    <t>International Journal of Computer Applications</t>
+  </si>
+  <si>
+    <t>Foundation of Computer Science</t>
+  </si>
+  <si>
+    <t>The Journal of Immunology</t>
+  </si>
+  <si>
+    <t>American Association of Immunologists</t>
+  </si>
+  <si>
+    <t>Grassland in a changing world. European Grassland Federation</t>
+  </si>
+  <si>
+    <t>Annals of Arid Zone</t>
+  </si>
+  <si>
+    <t>13th World Conference on Earthquake Engineering Vancouver, Paper</t>
+  </si>
+  <si>
+    <t>Journal of Energy, Heat and Mass Transfer</t>
+  </si>
+  <si>
+    <t>Hyperfine Interactions</t>
+  </si>
+  <si>
+    <t>Kluwer Academic Publishers</t>
+  </si>
+  <si>
+    <t>Society and Culture</t>
+  </si>
+  <si>
+    <t>Institute of Social Studies.</t>
+  </si>
+  <si>
+    <t>Forsch Ingenieurwes</t>
+  </si>
+  <si>
+    <t>Indian Journal of Agroforestry</t>
+  </si>
+  <si>
+    <t>Cluster Computing</t>
   </si>
 </sst>
 </file>
@@ -720,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="2" width="124.3046875" customWidth="1"/>
@@ -738,9 +1050,651 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
